--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_156_R16.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_156_R16.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9447</v>
+        <v>4.6952</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6132</v>
+        <v>4.8006</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3315</v>
+        <v>-0.1054</v>
       </c>
       <c r="G2" t="n">
         <v>3.6581</v>
@@ -610,13 +610,13 @@
         <v>1.1598</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4516</v>
+        <v>1.2021</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0355</v>
+        <v>1.223</v>
       </c>
       <c r="U2" t="n">
-        <v>0.416</v>
+        <v>-0.0209</v>
       </c>
       <c r="V2" t="n">
         <v>-1.3247</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6848</v>
+        <v>2.6854</v>
       </c>
       <c r="E3" t="n">
-        <v>2.517</v>
+        <v>1.2824</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1678</v>
+        <v>1.4031</v>
       </c>
       <c r="G3" t="n">
         <v>1.305</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6118</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8758</v>
+        <v>0.6411</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.264</v>
+        <v>-0.0288</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8467</v>
+        <v>1.5756</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5127</v>
+        <v>-0.4813</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3594</v>
+        <v>2.057</v>
       </c>
       <c r="G4" t="n">
         <v>0.531</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3879</v>
+        <v>0.1169</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1098</v>
+        <v>-0.0784</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4977</v>
+        <v>0.1953</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.6663</v>
+        <v>-1.1226</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1028</v>
+        <v>-1.7608</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4366</v>
+        <v>0.6382</v>
       </c>
       <c r="G5" t="n">
         <v>-0.131</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-0.3833</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4086</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5184</v>
+        <v>-0.3167</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0722</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8946</v>
+        <v>-1.3086</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8004</v>
+        <v>-1.9119</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9058</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8935999999999999</v>
@@ -922,13 +922,13 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3025</v>
+        <v>-0.7165</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5683</v>
+        <v>-0.6798</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2658</v>
+        <v>-0.0367</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3943</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>J. RHODEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8959</v>
+        <v>-1.3467</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7711</v>
+        <v>-1.9421</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1249</v>
+        <v>0.5954</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.0416</v>
+        <v>1.2548</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4585</v>
+        <v>-1.6963</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.5831</v>
+        <v>2.9512</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5865</v>
+        <v>2.6062</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6253</v>
+        <v>-0.9271</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.2118</v>
+        <v>3.5333</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4551</v>
+        <v>-1.3513</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0838</v>
+        <v>-0.7692</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3713</v>
+        <v>-0.5821</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6237</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.478</v>
+        <v>-0.0501</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1845</v>
+        <v>0.0907</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2934</v>
+        <v>-0.1408</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RHODEN</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4419</v>
+        <v>-1.8287</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0037</v>
+        <v>-1.7711</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5618</v>
+        <v>-0.0577</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2548</v>
+        <v>-3.0416</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6963</v>
+        <v>-0.4585</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9512</v>
+        <v>-2.5831</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6062</v>
+        <v>-1.5865</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9271</v>
+        <v>0.6253</v>
       </c>
       <c r="L8" t="n">
-        <v>3.5333</v>
+        <v>-2.2118</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3513</v>
+        <v>-1.4551</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7692</v>
+        <v>-1.0838</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5821</v>
+        <v>-0.3713</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1453</v>
+        <v>-0.4107</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9709</v>
+        <v>-0.1845</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1744</v>
+        <v>-0.2262</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7682</v>
+        <v>-2.2421</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4595</v>
+        <v>-2.6944</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3087</v>
+        <v>0.4523</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3645</v>
+        <v>-2.1262</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7322</v>
+        <v>-1.0755</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6323</v>
+        <v>-1.0506</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7023</v>
+        <v>-2.2582</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7023</v>
+        <v>-0.6855</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.5727</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6622</v>
+        <v>0.1321</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0299</v>
+        <v>-0.39</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6323</v>
+        <v>0.5221</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1718</v>
+        <v>-0.8118</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5975</v>
+        <v>-0.4362</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4257</v>
+        <v>-0.3756</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9784</v>
+        <v>-2.3733</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2291</v>
+        <v>-2.031</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2507</v>
+        <v>-0.3423</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1262</v>
+        <v>-2.3645</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0755</v>
+        <v>-1.7322</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0506</v>
+        <v>-0.6323</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.2582</v>
+        <v>-0.7023</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6855</v>
+        <v>-0.7023</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5727</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1321</v>
+        <v>-1.6622</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.39</v>
+        <v>-1.0299</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5221</v>
+        <v>-0.6323</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5481</v>
+        <v>0.2232</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9709</v>
+        <v>-0.1689</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5772</v>
+        <v>0.3921</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3017</v>
+        <v>-5.9239</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2752</v>
+        <v>-2.9646</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0265</v>
+        <v>-2.9593</v>
       </c>
       <c r="G11" t="n">
         <v>-4.5841</v>
@@ -1312,13 +1312,13 @@
         <v>1.6237</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3207</v>
+        <v>0.0571</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1098</v>
+        <v>0.2008</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2109</v>
+        <v>-0.1436</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8608</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.6566</v>
+        <v>-6.4441</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0205</v>
+        <v>-4.0769</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6361</v>
+        <v>-2.3672</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0603</v>
@@ -1390,13 +1390,13 @@
         <v>1.1598</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9726</v>
+        <v>0.2399</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5975</v>
+        <v>0.3462</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3752</v>
+        <v>-0.1063</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1444</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.1274</v>
+        <v>-13.6338</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.0448</v>
+        <v>-13.5511</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.08260000000000067</v>
+        <v>-0.08259999999999978</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.4524</v>
+        <v>-7.452399999999999</v>
       </c>
       <c r="H13" t="n">
         <v>-6.398499999999999</v>
@@ -1450,13 +1450,13 @@
         <v>-1.539900000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-7.098100000000001</v>
+        <v>-7.0981</v>
       </c>
       <c r="N13" t="n">
         <v>-7.5846</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4861999999999997</v>
+        <v>0.4862000000000002</v>
       </c>
       <c r="P13" t="n">
         <v>0.000100000000000211</v>
@@ -1468,13 +1468,13 @@
         <v>15.0771</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4146</v>
+        <v>0.07919999999999994</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6065000000000002</v>
+        <v>0.8874000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8083</v>
+        <v>-0.8082</v>
       </c>
       <c r="V13" t="n">
         <v>-6.2603</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.4307</v>
+        <v>7.5747</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1081</v>
+        <v>3.4619</v>
       </c>
       <c r="F14" t="n">
-        <v>5.3226</v>
+        <v>4.1128</v>
       </c>
       <c r="G14" t="n">
         <v>4.2015</v>
@@ -1546,13 +1546,13 @@
         <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>1.925</v>
+        <v>1.069</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1845</v>
+        <v>0.1693</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1095</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>1.6083</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.2207</v>
+        <v>5.9404</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1437</v>
+        <v>4.9642</v>
       </c>
       <c r="F15" t="n">
-        <v>1.077</v>
+        <v>0.9762</v>
       </c>
       <c r="G15" t="n">
         <v>2.8268</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3913</v>
+        <v>0.1109</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8363</v>
+        <v>0.6567</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.445</v>
+        <v>-0.5458</v>
       </c>
       <c r="V15" t="n">
         <v>2.5387</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0177</v>
+        <v>5.2592</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6725</v>
+        <v>1.8469</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3452</v>
+        <v>3.4124</v>
       </c>
       <c r="G16" t="n">
         <v>1.785</v>
@@ -1702,13 +1702,13 @@
         <v>2.5515</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3539</v>
+        <v>0.5955</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2388</v>
+        <v>0.4132</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1151</v>
+        <v>0.1823</v>
       </c>
       <c r="V16" t="n">
         <v>1.719</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0279</v>
+        <v>3.7515</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3116</v>
+        <v>2.6654</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7164</v>
+        <v>1.086</v>
       </c>
       <c r="G17" t="n">
         <v>3.0855</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.988</v>
+        <v>-0.2645</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5975</v>
+        <v>-0.2436</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3905</v>
+        <v>-0.0209</v>
       </c>
       <c r="V17" t="n">
         <v>0.9304</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1062</v>
+        <v>1.9882</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4363</v>
+        <v>-0.5542</v>
       </c>
       <c r="F18" t="n">
         <v>2.5424</v>
@@ -1858,10 +1858,10 @@
         <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2636</v>
+        <v>0.1456</v>
       </c>
       <c r="U18" t="n">
         <v>0.6563</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. KEITA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4855</v>
+        <v>-0.3574</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1494</v>
+        <v>-2.0616</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3361</v>
+        <v>1.7042</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3361</v>
+        <v>1.4276</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3361</v>
+        <v>1.1031</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.3245</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.2493</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.9718</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.2775</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3361</v>
+        <v>0.1782</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3361</v>
+        <v>0.1313</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1494</v>
+        <v>-0.3058</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1494</v>
+        <v>0.2559</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.5616</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. KUSTURICA</t>
+          <t>S. KEITA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,28 +1969,28 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2718</v>
+        <v>-0.4855</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9357</v>
+        <v>-0.1494</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3361</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1224</v>
+        <v>-0.3361</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1224</v>
+        <v>-0.3361</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2745</v>
+        <v>-1.1401</v>
       </c>
       <c r="E21" t="n">
         <v>-2.87</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5955</v>
+        <v>1.7299</v>
       </c>
       <c r="G21" t="n">
         <v>0.5661</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.217</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.2161</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>N. KUSTURICA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4931</v>
+        <v>-1.2718</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9118</v>
+        <v>-0.9357</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4187</v>
+        <v>-0.3361</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5183</v>
+        <v>-1.1224</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8558</v>
+        <v>-1.1224</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6625</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.1678</v>
+        <v>-0.7863</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4551</v>
+        <v>-0.7863</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7127</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3505</v>
+        <v>-0.3361</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4008</v>
+        <v>-0.3361</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0502</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0444</v>
+        <v>-0.1494</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1142</v>
+        <v>-0.1494</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1586</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6529</v>
+        <v>-1.6954</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6514</v>
+        <v>-2.1477</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9984</v>
+        <v>0.4523</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4276</v>
+        <v>-2.5183</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1031</v>
+        <v>-1.8558</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3245</v>
+        <v>-0.6625</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2493</v>
+        <v>-2.1678</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9718</v>
+        <v>-1.4551</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2775</v>
+        <v>-0.7127</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1782</v>
+        <v>-0.3505</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1313</v>
+        <v>-0.4008</v>
       </c>
       <c r="O23" t="n">
-        <v>0.047</v>
+        <v>0.0502</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6012</v>
+        <v>-0.2467</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3339</v>
+        <v>-0.1217</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2674</v>
+        <v>-0.125</v>
       </c>
       <c r="V23" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6154</v>
+        <v>-2.11</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0872</v>
+        <v>-1.6154</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5282</v>
+        <v>-0.4946</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7872</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.756</v>
+        <v>-0.2506</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6721</v>
+        <v>-0.2003</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0839</v>
+        <v>-0.0503</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8825</v>
+        <v>-2.3264</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5755</v>
+        <v>-1.9857</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3071</v>
+        <v>-0.3407</v>
       </c>
       <c r="G25" t="n">
         <v>-0.8443000000000001</v>
@@ -2404,13 +2404,13 @@
         <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2702</v>
+        <v>0.286</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2592</v>
+        <v>0.3306</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.011</v>
+        <v>-0.0446</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>15.1275</v>
+        <v>15.1274</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6185999999999998</v>
+        <v>0.6186999999999991</v>
       </c>
       <c r="F26" t="n">
         <v>14.5087</v>
       </c>
       <c r="G26" t="n">
-        <v>7.452499999999999</v>
+        <v>7.452499999999997</v>
       </c>
       <c r="H26" t="n">
-        <v>6.398499999999999</v>
+        <v>6.398499999999998</v>
       </c>
       <c r="I26" t="n">
         <v>1.0538</v>
@@ -2461,7 +2461,7 @@
         <v>7.584399999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4860999999999999</v>
+        <v>-0.4861000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>0.3541999999999995</v>
@@ -2482,16 +2482,16 @@
         <v>15.077</v>
       </c>
       <c r="S26" t="n">
-        <v>1.414499999999999</v>
+        <v>1.4143</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8082000000000001</v>
+        <v>0.8081999999999998</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6061999999999999</v>
+        <v>0.6062000000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>6.260300000000001</v>
+        <v>6.260299999999999</v>
       </c>
       <c r="W26" t="n">
         <v>7.789</v>
